--- a/Perfil_Mentoria.xlsx
+++ b/Perfil_Mentoria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_E693E059F159B3A8EDF5CA209B888B5094EB2656" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50802D88-4FB2-400B-AB6E-14C486564B67}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_E693E059F159B3A8EDF5CA209B888B5094EB2656" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58C12EC3-CC31-4B60-B93C-280DC52D9DAF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7822,7 +7822,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:BU377"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -33957,7 +33956,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="179" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>1299</v>
       </c>
@@ -34112,7 +34111,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="180" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>1299</v>
       </c>
@@ -34225,7 +34224,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="181" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>1299</v>
       </c>
@@ -34356,7 +34355,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="182" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>1299</v>
       </c>
@@ -34493,7 +34492,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="183" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>1299</v>
       </c>
@@ -34624,7 +34623,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="184" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>1299</v>
       </c>
@@ -34755,7 +34754,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="185" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>1299</v>
       </c>
@@ -34910,7 +34909,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="186" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>1299</v>
       </c>
@@ -35047,7 +35046,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="187" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>1299</v>
       </c>
@@ -35178,7 +35177,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="188" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>1299</v>
       </c>
@@ -35303,7 +35302,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="189" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>1299</v>
       </c>
@@ -35443,7 +35442,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="190" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>1299</v>
       </c>
@@ -35562,7 +35561,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="191" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>1299</v>
       </c>
@@ -35687,7 +35686,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="192" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1299</v>
       </c>
@@ -35824,7 +35823,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="193" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1299</v>
       </c>
@@ -35955,7 +35954,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="194" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1299</v>
       </c>
@@ -36086,7 +36085,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="195" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1299</v>
       </c>
@@ -36244,7 +36243,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="196" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1299</v>
       </c>
@@ -36375,7 +36374,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="197" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1299</v>
       </c>
@@ -36500,7 +36499,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="198" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1299</v>
       </c>
@@ -36625,7 +36624,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="199" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1299</v>
       </c>
@@ -36765,7 +36764,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="200" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1299</v>
       </c>
@@ -36950,7 +36949,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="201" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1299</v>
       </c>
@@ -37087,7 +37086,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="202" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1299</v>
       </c>
@@ -37212,7 +37211,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="203" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1299</v>
       </c>
@@ -37349,7 +37348,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="204" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1299</v>
       </c>
@@ -37486,7 +37485,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="205" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1299</v>
       </c>
@@ -37605,7 +37604,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="206" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1299</v>
       </c>
@@ -37742,7 +37741,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="207" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1299</v>
       </c>
@@ -37867,7 +37866,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="208" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1299</v>
       </c>
@@ -38004,7 +38003,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="209" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>1299</v>
       </c>
@@ -38135,7 +38134,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="210" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>1299</v>
       </c>
@@ -38266,7 +38265,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="211" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1299</v>
       </c>
@@ -38403,7 +38402,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="212" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1299</v>
       </c>
@@ -38558,7 +38557,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="213" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>1299</v>
       </c>
@@ -38713,7 +38712,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="214" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>1299</v>
       </c>
@@ -38871,7 +38870,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="215" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1299</v>
       </c>
@@ -38999,7 +38998,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="216" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>1299</v>
       </c>
@@ -39130,7 +39129,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="217" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1299</v>
       </c>
@@ -39288,7 +39287,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="218" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>1299</v>
       </c>
@@ -39419,7 +39418,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="219" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>1299</v>
       </c>
@@ -39586,7 +39585,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="220" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1299</v>
       </c>
@@ -39741,7 +39740,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="221" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>1299</v>
       </c>
@@ -39866,7 +39865,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="222" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>1299</v>
       </c>
@@ -40003,7 +40002,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="223" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1299</v>
       </c>
@@ -40128,7 +40127,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="224" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>1299</v>
       </c>
@@ -40265,7 +40264,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="225" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1299</v>
       </c>
@@ -40423,7 +40422,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="226" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1299</v>
       </c>
@@ -40548,7 +40547,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="227" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1299</v>
       </c>
@@ -40673,7 +40672,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="228" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1299</v>
       </c>
@@ -40804,7 +40803,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="229" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1299</v>
       </c>
@@ -40929,7 +40928,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="230" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1299</v>
       </c>
@@ -41066,7 +41065,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="231" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1299</v>
       </c>
@@ -41185,7 +41184,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="232" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1299</v>
       </c>
@@ -41334,7 +41333,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="233" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1299</v>
       </c>
@@ -41516,7 +41515,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="234" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1299</v>
       </c>
@@ -41653,7 +41652,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="235" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1299</v>
       </c>
@@ -41820,7 +41819,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="236" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1299</v>
       </c>
@@ -41960,7 +41959,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="237" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1299</v>
       </c>
@@ -42088,7 +42087,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="238" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1299</v>
       </c>
@@ -42225,7 +42224,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="239" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1299</v>
       </c>
@@ -42350,7 +42349,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="240" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1299</v>
       </c>
@@ -42475,7 +42474,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="241" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1299</v>
       </c>
@@ -42600,7 +42599,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="242" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1299</v>
       </c>
@@ -42737,7 +42736,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="243" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1299</v>
       </c>
@@ -42865,7 +42864,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="244" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1299</v>
       </c>
@@ -42990,7 +42989,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="245" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1299</v>
       </c>
@@ -43121,7 +43120,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="246" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1299</v>
       </c>
@@ -43246,7 +43245,7 @@
         <v>2476</v>
       </c>
     </row>
-    <row r="247" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1299</v>
       </c>
@@ -43395,7 +43394,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="248" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1299</v>
       </c>
@@ -43520,7 +43519,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="249" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1299</v>
       </c>
@@ -43639,7 +43638,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="250" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1299</v>
       </c>
@@ -43779,7 +43778,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="251" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1299</v>
       </c>
@@ -43916,7 +43915,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="252" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1299</v>
       </c>
@@ -44041,7 +44040,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="253" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1299</v>
       </c>
@@ -44166,7 +44165,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="254" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1299</v>
       </c>
@@ -44297,7 +44296,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="255" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1299</v>
       </c>
@@ -44422,7 +44421,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="256" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1299</v>
       </c>
@@ -44553,7 +44552,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="257" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1299</v>
       </c>
@@ -44678,7 +44677,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="258" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1299</v>
       </c>
@@ -44827,7 +44826,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="259" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1299</v>
       </c>
@@ -44967,7 +44966,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="260" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1299</v>
       </c>
@@ -45098,7 +45097,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="261" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1299</v>
       </c>
@@ -45238,7 +45237,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="262" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1299</v>
       </c>
@@ -45375,7 +45374,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="263" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1299</v>
       </c>
@@ -45506,7 +45505,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="264" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1299</v>
       </c>
@@ -45637,7 +45636,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="265" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1299</v>
       </c>
@@ -45774,7 +45773,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="266" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1299</v>
       </c>
@@ -45917,7 +45916,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="267" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1299</v>
       </c>
@@ -46048,7 +46047,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="268" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1299</v>
       </c>
@@ -46188,7 +46187,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="269" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1299</v>
       </c>
@@ -46328,7 +46327,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="270" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1299</v>
       </c>
@@ -46465,7 +46464,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="271" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1299</v>
       </c>
@@ -46602,7 +46601,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="272" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1299</v>
       </c>
@@ -46733,7 +46732,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="273" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1299</v>
       </c>
@@ -46852,7 +46851,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="274" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1299</v>
       </c>
@@ -46992,7 +46991,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="275" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1299</v>
       </c>
@@ -47123,7 +47122,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="276" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1299</v>
       </c>
@@ -47263,7 +47262,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="277" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1299</v>
       </c>
@@ -47427,7 +47426,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="278" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1299</v>
       </c>
@@ -47561,7 +47560,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="279" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1299</v>
       </c>
@@ -47716,7 +47715,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="280" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1299</v>
       </c>
@@ -47856,7 +47855,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="281" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1299</v>
       </c>
@@ -48002,7 +48001,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="282" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1299</v>
       </c>
@@ -48133,7 +48132,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="283" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1299</v>
       </c>
@@ -48261,7 +48260,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="284" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1299</v>
       </c>
@@ -48380,7 +48379,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="285" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1299</v>
       </c>
@@ -48499,7 +48498,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="286" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1299</v>
       </c>
@@ -48642,7 +48641,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="287" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1299</v>
       </c>
@@ -48800,7 +48799,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="288" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1299</v>
       </c>
@@ -48949,7 +48948,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="289" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1299</v>
       </c>
@@ -49089,7 +49088,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="290" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1299</v>
       </c>
@@ -49220,7 +49219,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="291" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1299</v>
       </c>
@@ -49414,7 +49413,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="292" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1299</v>
       </c>
@@ -49533,7 +49532,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="293" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>1299</v>
       </c>
@@ -49664,7 +49663,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="294" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1299</v>
       </c>
@@ -49783,7 +49782,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="295" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1299</v>
       </c>
@@ -49959,7 +49958,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="296" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1299</v>
       </c>
@@ -50090,7 +50089,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="297" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1299</v>
       </c>
@@ -50233,7 +50232,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="298" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1299</v>
       </c>
@@ -50364,7 +50363,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="299" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1299</v>
       </c>
@@ -50489,7 +50488,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="300" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1299</v>
       </c>
@@ -50635,7 +50634,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="301" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1299</v>
       </c>
@@ -50772,7 +50771,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="302" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1299</v>
       </c>
@@ -50909,7 +50908,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="303" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1299</v>
       </c>
@@ -51040,7 +51039,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="304" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1299</v>
       </c>
@@ -51165,7 +51164,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="305" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1299</v>
       </c>
@@ -51302,7 +51301,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="306" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1299</v>
       </c>
@@ -51418,7 +51417,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="307" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1299</v>
       </c>
@@ -51534,7 +51533,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="308" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1299</v>
       </c>
@@ -51659,7 +51658,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="309" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1299</v>
       </c>
@@ -51805,7 +51804,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="310" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1299</v>
       </c>
@@ -51933,7 +51932,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="311" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1299</v>
       </c>
@@ -52061,7 +52060,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="312" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1299</v>
       </c>
@@ -52192,7 +52191,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="313" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1299</v>
       </c>
@@ -52302,7 +52301,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="314" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1299</v>
       </c>
@@ -52409,7 +52408,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="315" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1299</v>
       </c>
@@ -52516,7 +52515,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="316" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1299</v>
       </c>
@@ -52629,7 +52628,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="317" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1299</v>
       </c>
@@ -52748,7 +52747,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="318" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1299</v>
       </c>
@@ -52873,7 +52872,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="319" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1299</v>
       </c>
@@ -52992,7 +52991,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="320" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1299</v>
       </c>
@@ -53111,7 +53110,7 @@
         <v>2357</v>
       </c>
     </row>
-    <row r="321" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>1299</v>
       </c>
@@ -53239,7 +53238,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="322" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1299</v>
       </c>
@@ -53364,7 +53363,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="323" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1299</v>
       </c>
@@ -53483,7 +53482,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="324" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>1299</v>
       </c>
@@ -53611,7 +53610,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="325" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1299</v>
       </c>
@@ -53727,7 +53726,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="326" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1299</v>
       </c>
@@ -53840,7 +53839,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="327" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1299</v>
       </c>
@@ -53971,7 +53970,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="328" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1299</v>
       </c>
@@ -54096,7 +54095,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="329" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1299</v>
       </c>
@@ -54212,7 +54211,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="330" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1299</v>
       </c>
@@ -54349,7 +54348,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="331" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1299</v>
       </c>
@@ -54480,7 +54479,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="332" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1299</v>
       </c>
@@ -54608,7 +54607,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="333" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1299</v>
       </c>
@@ -54742,7 +54741,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="334" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1299</v>
       </c>
@@ -54876,7 +54875,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="335" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1299</v>
       </c>
@@ -54995,7 +54994,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="336" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1299</v>
       </c>
@@ -55111,7 +55110,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="337" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1299</v>
       </c>
@@ -55236,7 +55235,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="338" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1299</v>
       </c>
@@ -55349,7 +55348,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="339" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1299</v>
       </c>
@@ -55471,7 +55470,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="340" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1299</v>
       </c>
@@ -55593,7 +55592,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="341" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1299</v>
       </c>
@@ -55721,7 +55720,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="342" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1299</v>
       </c>
@@ -55852,7 +55851,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="343" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1299</v>
       </c>
@@ -55971,7 +55970,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="344" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1299</v>
       </c>
@@ -56090,7 +56089,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="345" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1299</v>
       </c>
@@ -56203,7 +56202,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="346" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1299</v>
       </c>
@@ -56325,7 +56324,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="347" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1299</v>
       </c>
@@ -56459,7 +56458,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="348" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1299</v>
       </c>
@@ -56590,7 +56589,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="349" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1299</v>
       </c>
@@ -56700,7 +56699,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="350" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1299</v>
       </c>
@@ -56813,7 +56812,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="351" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1299</v>
       </c>
@@ -56929,7 +56928,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="352" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1299</v>
       </c>
@@ -57048,7 +57047,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="353" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1299</v>
       </c>
@@ -57182,7 +57181,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="354" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1299</v>
       </c>
@@ -57301,7 +57300,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="355" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1299</v>
       </c>
@@ -57423,7 +57422,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="356" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1299</v>
       </c>
@@ -57560,7 +57559,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="357" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1299</v>
       </c>
@@ -57691,7 +57690,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="358" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1299</v>
       </c>
@@ -57831,7 +57830,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="359" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1299</v>
       </c>
@@ -57968,7 +57967,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="360" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1299</v>
       </c>
@@ -58126,7 +58125,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="361" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1299</v>
       </c>
@@ -58257,7 +58256,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="362" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1299</v>
       </c>
@@ -58403,7 +58402,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="363" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1299</v>
       </c>
@@ -58528,7 +58527,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="364" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1299</v>
       </c>
@@ -58668,7 +58667,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="365" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1299</v>
       </c>
@@ -58814,7 +58813,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="366" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1299</v>
       </c>
@@ -58951,7 +58950,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="367" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1299</v>
       </c>
@@ -59082,7 +59081,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="368" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1299</v>
       </c>
@@ -59219,7 +59218,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="369" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1299</v>
       </c>
@@ -59353,7 +59352,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="370" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1299</v>
       </c>
@@ -59490,7 +59489,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="371" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>1299</v>
       </c>
@@ -59621,7 +59620,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="372" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1299</v>
       </c>
@@ -59746,7 +59745,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="373" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>1299</v>
       </c>
@@ -59886,7 +59885,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="374" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>1299</v>
       </c>
@@ -60023,7 +60022,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="375" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>1299</v>
       </c>
@@ -60163,7 +60162,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="376" spans="1:73" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>1299</v>
       </c>
@@ -60445,11 +60444,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:BU377" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Monapo"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BU377">
       <sortCondition ref="BU1:BU377"/>
     </sortState>
@@ -60459,6 +60453,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
@@ -60467,15 +60470,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60714,20 +60708,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7703B566-3A82-4514-9901-3E0C0621FFDB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00155AD8-3A1A-4444-A31D-F84F7FB1972B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
     <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7703B566-3A82-4514-9901-3E0C0621FFDB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
